--- a/Digital-Business-Toolkit/09-Extras/Product.xlsx
+++ b/Digital-Business-Toolkit/09-Extras/Product.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Main Workspace" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Quick Start" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="User Guide" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="לוח בקרה" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="שולחן עבודה" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="התחלה מהירה" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="מדריך שימוש" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -647,7 +647,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Change Order &amp; Extras Manager — Dashboard</t>
+          <t>לוח בקרה — ניהול תוספות וחריגים</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -658,7 +658,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ContractorOS — Get paid for every extra you did</t>
+          <t>ContractorOS — קבלו תשלום על כל תוספת שביצעתם</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -695,42 +695,42 @@
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="B6" s="6">
-        <f>SUM('Main Workspace'!G4:G38)</f>
+        <f>SUM('שולחן עבודה'!G4:G38)</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>SUMIF('Main Workspace'!H4:H38,"אושר",'Main Workspace'!G4:G38)</f>
+        <f>SUMIF('שולחן עבודה'!H4:H38,"אושר",'שולחן עבודה'!G4:G38)</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>COUNTIF('Main Workspace'!H4:H38,"ממתין לאישור")</f>
+        <f>COUNTIF('שולחן עבודה'!H4:H38,"ממתין לאישור")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>SUMIFS('Main Workspace'!G4:G38,'Main Workspace'!I4:I38,"הושלם",'Main Workspace'!J4:J38,"לא")</f>
+        <f>SUMIFS('שולחן עבודה'!G4:G38,'שולחן עבודה'!I4:I38,"הושלם",'שולחן עבודה'!J4:J38,"לא")</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>SUMIFS('Main Workspace'!G4:G38,'Main Workspace'!J4:J38,"כן",'Main Workspace'!K4:K38,"לא")</f>
+        <f>SUMIFS('שולחן עבודה'!G4:G38,'שולחן עבודה'!J4:J38,"כן",'שולחן עבודה'!K4:K38,"לא")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>⚠ Business Insights / התראות</t>
+          <t>⚠ תובנות עסקיות והתראות</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="8">
-        <f>IF(COUNTIF('Main Workspace'!H4:H38,"ממתין לאישור")&gt;0,"יש "&amp;COUNTIF('Main Workspace'!H4:H38,"ממתין לאישור")&amp;" תוספות ממתינות לאישור לקוח.","כל התוספות טופלו מבחינת אישור.")</f>
+        <f>IF(COUNTIF('שולחן עבודה'!H4:H38,"ממתין לאישור")&gt;0,"יש "&amp;COUNTIF('שולחן עבודה'!H4:H38,"ממתין לאישור")&amp;" תוספות ממתינות לאישור לקוח.","כל התוספות טופלו מבחינת אישור.")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="9">
-        <f>IF(SUMIFS('Main Workspace'!G4:G38,'Main Workspace'!I4:I38,"הושלם",'Main Workspace'!J4:J38,"לא")&gt;0,"יש עבודות תוספת שהושלמו אך טרם חויבו — כסף שממתין על השולחן!","כל העבודות שהושלמו כבר חויבו.")</f>
+        <f>IF(SUMIFS('שולחן עבודה'!G4:G38,'שולחן עבודה'!I4:I38,"הושלם",'שולחן עבודה'!J4:J38,"לא")&gt;0,"יש עבודות תוספת שהושלמו אך טרם חויבו — כסף שממתין על השולחן!","כל העבודות שהושלמו כבר חויבו.")</f>
         <v/>
       </c>
     </row>
@@ -773,7 +773,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>ניהול תוספות וחריגים | Change Order &amp; Extras Manager</t>
+          <t>ניהול תוספות וחריגים</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>פרויקט</t>
+          <t>שם פרויקט</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>PRJ-0001</t>
+          <t>שיפוץ מטבח - וילה כהן</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>PRJ-0001</t>
+          <t>שיפוץ מטבח - וילה כהן</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>PRJ-0002</t>
+          <t>החלפת לוח חשמל</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>PRJ-0004</t>
+          <t>איטום גג</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>PRJ-0005</t>
+          <t>ריצוף חדר אמבטיה</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -1688,7 +1688,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>התחלה מהירה | Quick Start</t>
+          <t>התחלה מהירה</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1704,7 +1704,7 @@
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>1. עברו ללשונית 'Main Workspace'.</t>
+          <t>1. עברו ללשונית 'שולחן עבודה'.</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="21" t="inlineStr">
         <is>
-          <t>5. עברו ל-Dashboard לוודא שאין עבודות שהושלמו בלי לחייב עליהן.</t>
+          <t>5. עברו ל-לוח הבקרה לוודא שאין עבודות שהושלמו בלי לחייב עליהן.</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>מדריך שימוש | User Guide</t>
+          <t>מדריך שימוש</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>כלי למעקב אחר תוספות ושינויים מעבר להצעת המחיר המקורית (Change Orders).</t>
+          <t>כלי למעקב אחר תוספות ושינויים מעבר להצעת המחיר המקורית.</t>
         </is>
       </c>
     </row>
@@ -1859,14 +1859,14 @@
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>סה"כ לכל תוספת (כמות × מחיר), וכל מדדי ה-Dashboard.</t>
+          <t>סה"כ לכל תוספת (כמות × מחיר), וכל מדדי לוח הבקרה.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>מה Dashboard מציג?</t>
+          <t>מה לוח הבקרה מציג?</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -1890,7 +1890,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>שאלות נפוצות (FAQ)</t>
+          <t>שאלות נפוצות</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>דרך עמודת 'פרויקט' (מספר הפרויקט), כך שאפשר לראות את כל התוספות של פרויקט מסוים.</t>
+          <t>דרך עמודת 'פרויקט' (שם הפרויקט), כך שאפשר לראות את כל התוספות של פרויקט מסוים — חשוב להקליד את השם זהה לכל המוצרים האחרים.</t>
         </is>
       </c>
     </row>

--- a/Digital-Business-Toolkit/09-Extras/Product.xlsx
+++ b/Digital-Business-Toolkit/09-Extras/Product.xlsx
@@ -658,7 +658,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ContractorOS — קבלו תשלום על כל תוספת שביצעתם</t>
+          <t>JobMargin — קבלו תשלום על כל תוספת שביצעתם</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
